--- a/Test Files/IndentMe.xlsx
+++ b/Test Files/IndentMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jamasoftware-my.sharepoint.com/personal/pknowles_jamasoftware_com/Documents/Documents/Coding/Excel-Indent-Tool/Test Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{3B43EBBB-66E4-45CE-B013-7496D3408D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA80E7B9-5F3D-459E-B14A-7691CEA572CE}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{3B43EBBB-66E4-45CE-B013-7496D3408D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACA7B6C-8891-4419-8209-F749BB5ECD93}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="20880" xr2:uid="{80D9136B-FFEB-4A0F-B849-239EF69949ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{80D9136B-FFEB-4A0F-B849-239EF69949ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>Heading</t>
   </si>
@@ -63,6 +63,24 @@
   </si>
   <si>
     <t>1.2 Subtitle</t>
+  </si>
+  <si>
+    <t>Heading 2</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>1.1.2</t>
+  </si>
+  <si>
+    <t>1.1.1.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1</t>
+  </si>
+  <si>
+    <t>1.2.1</t>
   </si>
 </sst>
 </file>
@@ -127,10 +145,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -453,7 +467,8 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="4" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
@@ -462,8 +477,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -476,7 +491,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="4">
@@ -490,7 +505,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="4">
@@ -504,6 +519,9 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" s="4">
         <v>2</v>
       </c>
@@ -515,6 +533,9 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C5" s="4">
         <v>3</v>
       </c>
@@ -526,6 +547,9 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
@@ -537,6 +561,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="C7" s="4">
         <v>3</v>
       </c>
@@ -548,6 +575,9 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
+      <c r="B8" s="4">
+        <v>1.2</v>
+      </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
@@ -558,6 +588,9 @@
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C9" s="4">
         <v>2</v>
